--- a/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FCC6A18-BAE1-45BF-8D45-1E1A6567A9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D121BCD4-03A9-408E-AAAA-F44448AD27C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="13" activeTab="15" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
   </bookViews>
   <sheets>
     <sheet name="UIVerification-RegisterPayPage" sheetId="1" r:id="rId1"/>
@@ -119,13 +119,253 @@
     <t>Arlington</t>
   </si>
   <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>t476640@deluxe.com</t>
+  </si>
+  <si>
+    <t>Account Profile,
+* Indicates required field,
+Company Name:,	
+First Name:,	
+Last Name:,	
+Address Line 1: *,	
+Address Line 2: ,  	
+Country: *,	
+ZIP: *,	
+City: *	,
+State : *,</t>
+  </si>
+  <si>
+    <t>Vaddahun Corp</t>
+  </si>
+  <si>
+    <t>MCGALLIARD</t>
+  </si>
+  <si>
+    <t>1645 FOX ST</t>
+  </si>
+  <si>
+    <t>Concover</t>
+  </si>
+  <si>
+    <t>Bharat</t>
+  </si>
+  <si>
+    <t>TABATHA</t>
+  </si>
+  <si>
+    <t>Fri Dec 12 17:26:02 IST 2025</t>
+  </si>
+  <si>
+    <t>DULIP</t>
+  </si>
+  <si>
+    <t>EKANAYAKE</t>
+  </si>
+  <si>
+    <t>708 36TH AVE NW</t>
+  </si>
+  <si>
+    <t>Hickory</t>
+  </si>
+  <si>
+    <t>* Indicates required field,
+Role: *,	
+ What's this?,
+First Name: *,	
+Last Name: *,	
+Uername: *,	
+Password: *,	
+Password must be at least 8 characters long and no more than 16 characters long. Password must contain at least one alpha character and one numeric character.,
+Confirm Password: *,
+E-mail Address: *,	
+Confirm E-mail Address: *,	
+Email Delivery Options:,Check here to receive email from this site,
+Text Receipt Phone Number:,	
+Text Delivery Options:</t>
+  </si>
+  <si>
+    <t>AutoABPUser6210</t>
+  </si>
+  <si>
+    <t>Available Pending Bills,* Indicates required field,
+Step 1: Pay Your Pending Bills(s) By Checking One or More Checkboxes in the "Check to Pay" Column Below.,One bill found.,Display,
+results,,Check to Pay,Pending Bills,Due Date,Pay Date,Amount Due,Amount to Pay,Schedule to Pay,Check to Pay,AutoABPDemoBBGSCF6210,UDF1:*,UDF2:*,UDF3:,UDF4:,	
+1 bills selected for payment, totaling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Step 4: Review Payment Plan,
+Amount due will be paid 3 calendar days before the Due Date,
+Step 5: Review Your Convenience Fees,
+Individual Convenience Fee Amount:,	
+Total Convenience Fees Paid:,	
+Total Paid under this plan:	</t>
+  </si>
+  <si>
+    <t>Komal</t>
+  </si>
+  <si>
+    <t>Step 1: Review bill to pay,
+Pending Bills,Due Date,Date Submitted,Date Modified,Amount Due,Amount to Pay,Balance Due,
+AutoABPDemoBBGDCF6211,	 	 	
+UDF1:*,	
+UDF2:,	
+UDF3:,
+UDF4:</t>
+  </si>
+  <si>
+    <t>Mon Dec 15 18:18:53 IST 2025</t>
+  </si>
+  <si>
+    <t>VTList1</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 00:42:47 IST 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Payment Plan Frequency,
+Annual,
+Select the date you wish to submit your first payment and it will recur every year on that day,
+Divide your payment plan by...,
+Number of Payments:,Divide the Balance Due into,
+Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on </t>
+  </si>
+  <si>
+    <t>Tue Dec 16 16:05:37 IST 2025</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>CFAmount</t>
+  </si>
+  <si>
+    <t>ReviewConvinienceFee</t>
+  </si>
+  <si>
+    <t>Select Payment Plan Frequency,
+Daily,
+Select the date you wish to submit your first payment and it will recur every day after,
+Divide your payment plan by...,
+Number of Payments:,Divide the Balance Due into ,
+Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
+Step 4: Review Payment Plan,
+1 Daily payment of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 16:28:03 IST 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Payment Plan Frequency,
+Quarterly,
+Select the date you wish to submit your first payment and it will recur every three months on that day,
+Note: Any payments associated with the payment plan that are scheduled on a date that does not exist (eg. February 30th, April 31st), will be processed on the first day of the following month.,
+Divide your payment plan by...,
+Number of Payments:,Divide the Balance Due into, 
+Individual Amount:,	Repeat this amount until the Balance Due is achieved: $ ,
+Step 4: Review Payment Plan
+1 Quarterly payment of $12.00 on </t>
+  </si>
+  <si>
+    <t>Tue Dec 16 17:14:35 IST 2025</t>
+  </si>
+  <si>
+    <t>Select the date you wish to submit your payment,Divide your payment plan by...,
+ Number of Payments:,	Divide the Balance Due into 
+,payments,
+ Individual Amount:,	Repeat this amount until the Balance Due is achieved: $, 
+12.00,
+Step 4: Review Payment Plan,
+1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 19:12:40 IST 2025</t>
+  </si>
+  <si>
+    <t>Recurring Fixed Amount Payment - The same amount is paid at a determined frequency.,
+ Automatic Payment - Bills are automatically paid 3 calendar days before the Due Date.,Select Payment Plan Frequency,
+Daily,
+Select the date you wish to submit your first payment and it will recur every day after,
+Step 4: Review Payment Plan,
+Daily payments of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 22:54:05 IST 2025</t>
+  </si>
+  <si>
+    <t>Select Payment Plan Frequency,
+Deferred,
+Select the date you wish to submit your payment,
+Step 4: Review Payment Plan,
+1 Deferred payment of $</t>
+  </si>
+  <si>
+    <t>Tue Dec 16 23:00:25 IST 2025</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Password must be at least 8 characters long and no more than 32 characters long.,Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
+  </si>
+  <si>
+    <t>Komalmis</t>
+  </si>
+  <si>
+    <t>Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
+  </si>
+  <si>
+    <t>Komalmish@</t>
+  </si>
+  <si>
+    <t>Password must contain at least one alpha character and one numeric character.</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Oct 30 11:04:53 IST 2025</t>
+  </si>
+  <si>
+    <t>Username must be at least 6 characters long.</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:24:31 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 22:24:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 04 01:04:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 04 01:46:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 04 03:57:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 04 04:08:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Jul 04 04:16:45 IST 2026</t>
+  </si>
+  <si>
     <t>Create Account Profile,
 * Indicates required field,
 Bill Records Found,
 Bill Name,Due Date,Amount Due,
 AutoABPDemoBBG6207,07/10/2027,$11.00,
-Uername:,
-Uername cannot contain any spaces or special characters.,
+Username:,
+Username cannot contain any spaces or special characters.,
 Password:,
 Password must be at least 8 characters long and no more than 16 characters long. Password must contain at least one alpha character and one numeric character.,
 Confirm Password:,
@@ -144,246 +384,6 @@
 ZIP:,	
 City:,	
 State :</t>
-  </si>
-  <si>
-    <t>Email</t>
-  </si>
-  <si>
-    <t>UserName</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>t476640@deluxe.com</t>
-  </si>
-  <si>
-    <t>Account Profile,
-* Indicates required field,
-Company Name:,	
-First Name:,	
-Last Name:,	
-Address Line 1: *,	
-Address Line 2: ,  	
-Country: *,	
-ZIP: *,	
-City: *	,
-State : *,</t>
-  </si>
-  <si>
-    <t>Vaddahun Corp</t>
-  </si>
-  <si>
-    <t>MCGALLIARD</t>
-  </si>
-  <si>
-    <t>1645 FOX ST</t>
-  </si>
-  <si>
-    <t>Concover</t>
-  </si>
-  <si>
-    <t>Bharat</t>
-  </si>
-  <si>
-    <t>TABATHA</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 17:26:02 IST 2025</t>
-  </si>
-  <si>
-    <t>DULIP</t>
-  </si>
-  <si>
-    <t>EKANAYAKE</t>
-  </si>
-  <si>
-    <t>708 36TH AVE NW</t>
-  </si>
-  <si>
-    <t>Hickory</t>
-  </si>
-  <si>
-    <t>* Indicates required field,
-Role: *,	
- What's this?,
-First Name: *,	
-Last Name: *,	
-Uername: *,	
-Password: *,	
-Password must be at least 8 characters long and no more than 16 characters long. Password must contain at least one alpha character and one numeric character.,
-Confirm Password: *,
-E-mail Address: *,	
-Confirm E-mail Address: *,	
-Email Delivery Options:,Check here to receive email from this site,
-Text Receipt Phone Number:,	
-Text Delivery Options:</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 17:55:05 IST 2025</t>
-  </si>
-  <si>
-    <t>AutoABPUser6210</t>
-  </si>
-  <si>
-    <t>Available Pending Bills,* Indicates required field,
-Step 1: Pay Your Pending Bills(s) By Checking One or More Checkboxes in the "Check to Pay" Column Below.,One bill found.,Display,
-results,,Check to Pay,Pending Bills,Due Date,Pay Date,Amount Due,Amount to Pay,Schedule to Pay,Check to Pay,AutoABPDemoBBGSCF6210,UDF1:*,UDF2:*,UDF3:,UDF4:,	
-1 bills selected for payment, totaling</t>
-  </si>
-  <si>
-    <t>Fri Dec 12 19:34:24 IST 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Step 4: Review Payment Plan,
-Amount due will be paid 3 calendar days before the Due Date,
-Step 5: Review Your Convenience Fees,
-Individual Convenience Fee Amount:,	
-Total Convenience Fees Paid:,	
-Total Paid under this plan:	</t>
-  </si>
-  <si>
-    <t>Komal</t>
-  </si>
-  <si>
-    <t>Step 1: Review bill to pay,
-Pending Bills,Due Date,Date Submitted,Date Modified,Amount Due,Amount to Pay,Balance Due,
-AutoABPDemoBBGDCF6211,	 	 	
-UDF1:*,	
-UDF2:,	
-UDF3:,
-UDF4:</t>
-  </si>
-  <si>
-    <t>Mon Dec 15 18:18:53 IST 2025</t>
-  </si>
-  <si>
-    <t>VTList1</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 00:42:47 IST 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Payment Plan Frequency,
-Annual,
-Select the date you wish to submit your first payment and it will recur every year on that day,
-Divide your payment plan by...,
-Number of Payments:,Divide the Balance Due into,
-Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on </t>
-  </si>
-  <si>
-    <t>Tue Dec 16 16:05:37 IST 2025</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>CFAmount</t>
-  </si>
-  <si>
-    <t>ReviewConvinienceFee</t>
-  </si>
-  <si>
-    <t>Select Payment Plan Frequency,
-Daily,
-Select the date you wish to submit your first payment and it will recur every day after,
-Divide your payment plan by...,
-Number of Payments:,Divide the Balance Due into ,
-Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
-Step 4: Review Payment Plan,
-1 Daily payment of $</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 16:28:03 IST 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Payment Plan Frequency,
-Quarterly,
-Select the date you wish to submit your first payment and it will recur every three months on that day,
-Note: Any payments associated with the payment plan that are scheduled on a date that does not exist (eg. February 30th, April 31st), will be processed on the first day of the following month.,
-Divide your payment plan by...,
-Number of Payments:,Divide the Balance Due into, 
-Individual Amount:,	Repeat this amount until the Balance Due is achieved: $ ,
-Step 4: Review Payment Plan
-1 Quarterly payment of $12.00 on </t>
-  </si>
-  <si>
-    <t>Tue Dec 16 17:14:35 IST 2025</t>
-  </si>
-  <si>
-    <t>Select the date you wish to submit your payment,Divide your payment plan by...,
- Number of Payments:,	Divide the Balance Due into 
-,payments,
- Individual Amount:,	Repeat this amount until the Balance Due is achieved: $, 
-12.00,
-Step 4: Review Payment Plan,
-1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 19:12:40 IST 2025</t>
-  </si>
-  <si>
-    <t>Recurring Fixed Amount Payment - The same amount is paid at a determined frequency.,
- Automatic Payment - Bills are automatically paid 3 calendar days before the Due Date.,Select Payment Plan Frequency,
-Daily,
-Select the date you wish to submit your first payment and it will recur every day after,
-Step 4: Review Payment Plan,
-Daily payments of $</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 22:54:05 IST 2025</t>
-  </si>
-  <si>
-    <t>Select Payment Plan Frequency,
-Deferred,
-Select the date you wish to submit your payment,
-Step 4: Review Payment Plan,
-1 Deferred payment of $</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 23:00:25 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 20:47:47 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Dec 18 22:02:41 IST 2025</t>
-  </si>
-  <si>
-    <t>Password</t>
-  </si>
-  <si>
-    <t>Password must be at least 8 characters long and no more than 32 characters long.,Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
-  </si>
-  <si>
-    <t>Komalmis</t>
-  </si>
-  <si>
-    <t>Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
-  </si>
-  <si>
-    <t>Komalmish@</t>
-  </si>
-  <si>
-    <t>Password must contain at least one alpha character and one numeric character.</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Fri Dec 19 17:25:22 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 19 17:26:02 IST 2025</t>
-  </si>
-  <si>
-    <t>Fri Dec 19 17:26:28 IST 2025</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 11:04:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Username must be at least 6 characters long.</t>
   </si>
 </sst>
 </file>
@@ -934,7 +934,7 @@
         <v>398902</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>18</v>
@@ -983,41 +983,41 @@
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="269" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/20/2025</v>
+        <v>07/07/2026</v>
       </c>
       <c r="G2" s="16">
         <v>12</v>
@@ -1033,11 +1033,11 @@
  Individual Amount:,	Repeat this amount until the Balance Due is achieved: $, 
 12.00,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 12/20/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 12/20/2025</v>
+1 Deferred payment of $12.00 on 07/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026</v>
       </c>
       <c r="J2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(H2,"0.00")&amp;" starting on "&amp;F2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 12/20/2025</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1072,47 +1072,47 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="291.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>62</v>
+      <c r="A2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/20/2025</v>
+        <v>07/07/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1127,7 +1127,7 @@
 Daily,
 Select the date you wish to submit your first payment and it will recur every day after,
 Step 4: Review Payment Plan,
-Daily payments of $12.00 starting on 12/20/2025,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 12/20/2025 ,Individual Convenience Fee Amount:,	
+Daily payments of $12.00 starting on 07/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1135,7 +1135,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 12/20/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1164,47 +1164,47 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/20/2025</v>
+        <v>07/07/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1218,7 +1218,7 @@
 Deferred,
 Select the date you wish to submit your payment,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 12/20/2025,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 12/20/2025 ,Individual Convenience Fee Amount:,	
+1 Deferred payment of $12.00 on 07/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1226,7 +1226,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 12/20/2025 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1255,22 +1255,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1297,22 +1297,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1344,10 +1344,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>8</v>
@@ -1355,57 +1355,57 @@
     </row>
     <row r="2" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G2" s="19" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G4" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -1435,34 +1435,34 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1497,13 +1497,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>11</v>
@@ -1526,38 +1526,38 @@
     </row>
     <row r="2" spans="1:13" s="11" customFormat="1" ht="300" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="J2" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="M2" s="8">
         <v>28613</v>
@@ -1597,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H1" s="10" t="s">
         <v>11</v>
@@ -1625,39 +1625,39 @@
       </c>
     </row>
     <row r="2" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>40</v>
+      <c r="A2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>71</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>37</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>38</v>
       </c>
       <c r="M2" s="8">
         <v>28601</v>
@@ -1713,17 +1713,17 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>43</v>
+      <c r="A2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F2" s="12">
         <v>20262709</v>
@@ -1735,7 +1735,7 @@
         <v>8000010</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1765,7 +1765,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>8</v>
@@ -1773,20 +1773,20 @@
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1817,34 +1817,34 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="G1" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="175.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="175.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>47</v>
+      <c r="B2" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1875,10 +1875,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>8</v>
@@ -1886,20 +1886,20 @@
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G2" s="13" t="str">
         <f ca="1">F2&amp;TEXT(TODAY()+1,"mm/dd/yyyy")</f>
@@ -1908,7 +1908,7 @@
 Select the date you wish to submit your first payment and it will recur every year on that day,
 Divide your payment plan by...,
 Number of Payments:,Divide the Balance Due into,
-Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 12/20/2025</v>
+Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 07/07/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1940,47 +1940,47 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="241" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>12/20/2025</v>
+        <v>07/07/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1997,11 +1997,11 @@
 Number of Payments:,Divide the Balance Due into ,
 Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
 Step 4: Review Payment Plan,
-1 Daily payment of $12.00 on 12/20/2025,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 12/20/2025</v>
+1 Daily payment of $12.00 on 07/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/07/2026</v>
       </c>
       <c r="K2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 12/20/2025</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/07/2026</v>
       </c>
     </row>
   </sheetData>
@@ -2034,31 +2034,31 @@
         <v>3</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="250" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" t="s">
-        <v>58</v>
+      <c r="A2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>55</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">F2&amp;TEXT(TODAY()+1,"mm/dd/yyyy")</f>
@@ -2070,7 +2070,7 @@
 Number of Payments:,Divide the Balance Due into, 
 Individual Amount:,	Repeat this amount until the Balance Due is achieved: $ ,
 Step 4: Review Payment Plan
-1 Quarterly payment of $12.00 on 12/20/2025</v>
+1 Quarterly payment of $12.00 on 07/07/2026</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D121BCD4-03A9-408E-AAAA-F44448AD27C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF1C5DC-4DCD-45AC-9483-D31164230F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="13" activeTab="14" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
   </bookViews>
   <sheets>
     <sheet name="UIVerification-RegisterPayPage" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="85">
   <si>
     <t>Result</t>
   </si>
@@ -162,9 +162,6 @@
     <t>TABATHA</t>
   </si>
   <si>
-    <t>Fri Dec 12 17:26:02 IST 2025</t>
-  </si>
-  <si>
     <t>DULIP</t>
   </si>
   <si>
@@ -175,22 +172,6 @@
   </si>
   <si>
     <t>Hickory</t>
-  </si>
-  <si>
-    <t>* Indicates required field,
-Role: *,	
- What's this?,
-First Name: *,	
-Last Name: *,	
-Uername: *,	
-Password: *,	
-Password must be at least 8 characters long and no more than 16 characters long. Password must contain at least one alpha character and one numeric character.,
-Confirm Password: *,
-E-mail Address: *,	
-Confirm E-mail Address: *,	
-Email Delivery Options:,Check here to receive email from this site,
-Text Receipt Phone Number:,	
-Text Delivery Options:</t>
   </si>
   <si>
     <t>AutoABPUser6210</t>
@@ -222,13 +203,7 @@
 UDF4:</t>
   </si>
   <si>
-    <t>Mon Dec 15 18:18:53 IST 2025</t>
-  </si>
-  <si>
     <t>VTList1</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 00:42:47 IST 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Select Payment Plan Frequency,
@@ -237,9 +212,6 @@
 Divide your payment plan by...,
 Number of Payments:,Divide the Balance Due into,
 Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on </t>
-  </si>
-  <si>
-    <t>Tue Dec 16 16:05:37 IST 2025</t>
   </si>
   <si>
     <t>Amount</t>
@@ -259,9 +231,6 @@
 Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
 Step 4: Review Payment Plan,
 1 Daily payment of $</t>
-  </si>
-  <si>
-    <t>Tue Dec 16 16:28:03 IST 2025</t>
   </si>
   <si>
     <t xml:space="preserve">Select Payment Plan Frequency,
@@ -275,9 +244,6 @@
 1 Quarterly payment of $12.00 on </t>
   </si>
   <si>
-    <t>Tue Dec 16 17:14:35 IST 2025</t>
-  </si>
-  <si>
     <t>Select the date you wish to submit your payment,Divide your payment plan by...,
  Number of Payments:,	Divide the Balance Due into 
 ,payments,
@@ -287,9 +253,6 @@
 1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Tue Dec 16 19:12:40 IST 2025</t>
-  </si>
-  <si>
     <t>Recurring Fixed Amount Payment - The same amount is paid at a determined frequency.,
  Automatic Payment - Bills are automatically paid 3 calendar days before the Due Date.,Select Payment Plan Frequency,
 Daily,
@@ -298,9 +261,6 @@
 Daily payments of $</t>
   </si>
   <si>
-    <t>Tue Dec 16 22:54:05 IST 2025</t>
-  </si>
-  <si>
     <t>Select Payment Plan Frequency,
 Deferred,
 Select the date you wish to submit your payment,
@@ -308,55 +268,19 @@
 1 Deferred payment of $</t>
   </si>
   <si>
-    <t>Tue Dec 16 23:00:25 IST 2025</t>
-  </si>
-  <si>
     <t>Password</t>
   </si>
   <si>
-    <t>Password must be at least 8 characters long and no more than 32 characters long.,Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
-  </si>
-  <si>
     <t>Komalmis</t>
   </si>
   <si>
-    <t>Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
-  </si>
-  <si>
     <t>Komalmish@</t>
   </si>
   <si>
     <t>Password must contain at least one alpha character and one numeric character.</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu Oct 30 11:04:53 IST 2025</t>
-  </si>
-  <si>
-    <t>Username must be at least 6 characters long.</t>
-  </si>
-  <si>
-    <t>Fri Jul 03 22:24:31 IST 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 03 22:24:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 04 01:04:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 04 01:46:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 04 03:57:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 04 04:08:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Sat Jul 04 04:16:45 IST 2026</t>
   </si>
   <si>
     <t>Create Account Profile,
@@ -384,6 +308,100 @@
 ZIP:,	
 City:,	
 State :</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:20:36 IST 2026</t>
+  </si>
+  <si>
+    <t>* Indicates required field,
+Role: *,	
+ What's this?,
+First Name: *,	
+Last Name: *,	
+Username: *,	
+Password: *,	
+Password must be at least 8 characters long and no more than 16 characters long. Password must contain at least one alpha character and one numeric character.,
+Confirm Password: *,
+E-mail Address: *,	
+Confirm E-mail Address: *,	
+Email Delivery Options:,Check here to receive email from this site,
+Text Receipt Phone Number:,	
+Text Delivery Options:</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:27:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:29:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:30:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:32:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:33:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:34:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 15:44:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 18:02:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 18:10:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 18:12:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 18:14:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Please choose another user name</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 21:19:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 21:20:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Password must be at least 8 characters long and no more than 16 characters long.,Password must contain at least one alpha character and one numeric character.</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 21:26:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Jul 22 21:37:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:14:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:17:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:24:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:24:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 30 15:25:14 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -861,7 +879,7 @@
   <dimension ref="A1:P2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="19.26953125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" customWidth="true" width="19.26953125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -934,7 +952,7 @@
         <v>398902</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>18</v>
@@ -964,9 +982,9 @@
   <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="23.08984375" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="33" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="22.36328125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" customWidth="true" width="23.08984375" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="33.0" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" width="22.36328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="39" customHeight="1" x14ac:dyDescent="0.25">
@@ -983,41 +1001,41 @@
         <v>3</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="269" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>57</v>
+      <c r="B2" t="s" s="0">
+        <v>66</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/07/2026</v>
+        <v>07/23/2026</v>
       </c>
       <c r="G2" s="16">
         <v>12</v>
@@ -1033,11 +1051,11 @@
  Individual Amount:,	Repeat this amount until the Balance Due is achieved: $, 
 12.00,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 07/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026</v>
+1 Deferred payment of $12.00 on 07/23/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026</v>
       </c>
       <c r="J2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(H2,"0.00")&amp;" starting on "&amp;F2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1050,12 +1068,12 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="8.7265625" style="11" collapsed="1"/>
-    <col min="6" max="6" width="23.453125" style="11" customWidth="1" collapsed="1"/>
-    <col min="7" max="9" width="8.7265625" style="11" collapsed="1"/>
-    <col min="10" max="10" width="35" style="11" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="30.453125" style="11" customWidth="1" collapsed="1"/>
-    <col min="12" max="16384" width="8.7265625" style="11" collapsed="1"/>
+    <col min="1" max="5" style="11" width="8.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="11" width="23.453125" collapsed="true"/>
+    <col min="7" max="9" style="11" width="8.7265625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="11" width="35.0" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="11" width="30.453125" collapsed="true"/>
+    <col min="12" max="16384" style="11" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1075,22 +1093,22 @@
         <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="20" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I1" s="20" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J1" s="20" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="20" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="291.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1098,7 +1116,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1108,11 +1126,11 @@
         <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/07/2026</v>
+        <v>07/23/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1127,7 +1145,7 @@
 Daily,
 Select the date you wish to submit your first payment and it will recur every day after,
 Step 4: Review Payment Plan,
-Daily payments of $12.00 starting on 07/07/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
+Daily payments of $12.00 starting on 07/23/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1135,7 +1153,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1167,30 +1185,30 @@
         <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="409.5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>61</v>
+      <c r="B2" t="s" s="0">
+        <v>68</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1200,11 +1218,11 @@
         <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/07/2026</v>
+        <v>07/23/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1218,7 +1236,7 @@
 Deferred,
 Select the date you wish to submit your payment,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 07/07/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
+1 Deferred payment of $12.00 on 07/23/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1226,7 +1244,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/07/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1259,11 +1277,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" t="s">
-        <v>73</v>
+      <c r="A2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>80</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1301,11 +1319,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" t="s">
-        <v>74</v>
+      <c r="A2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>81</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1325,87 +1343,91 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="11.90625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="78.453125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" style="11" width="8.7265625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="11" width="25.36328125"/>
+    <col min="3" max="4" style="11" width="8.7265625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="11" width="11.90625" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="11" width="19.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="11" width="79.6328125" collapsed="true"/>
+    <col min="8" max="16384" style="11" width="8.7265625"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="14" t="s">
+      <c r="E1" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="52" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B2" t="s">
-        <v>75</v>
+    <row r="2" spans="1:7" ht="46" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>82</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>63</v>
+      <c r="G2" s="15" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="A3" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E3" t="s">
-        <v>64</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>65</v>
+      <c r="E3" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="A4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G4" t="s">
-        <v>67</v>
+      <c r="E4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1440,7 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="42.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="42.08984375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -1445,11 +1467,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>69</v>
+      <c r="B2" t="s" s="0">
+        <v>72</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1458,11 +1480,11 @@
       <c r="E2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G2" t="s">
-        <v>42</v>
+      <c r="F2" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1475,12 +1497,12 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="25.1796875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="10.08984375" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.90625" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="11.81640625" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="15.1796875" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12.08984375" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="25.1796875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="10.08984375" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" width="16.90625" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" width="11.81640625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" width="15.1796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="12.08984375" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="11" customFormat="1" ht="25" x14ac:dyDescent="0.25">
@@ -1525,11 +1547,11 @@
       </c>
     </row>
     <row r="2" spans="1:13" s="11" customFormat="1" ht="300" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
+      <c r="B2" t="s" s="0">
+        <v>58</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1573,14 +1595,14 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="16.36328125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.81640625" style="11" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.1796875" style="11" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="8.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="11" customWidth="1" collapsed="1"/>
-    <col min="5" max="11" width="16.36328125" style="11" collapsed="1"/>
-    <col min="12" max="12" width="10.1796875" style="11" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="9.54296875" style="11" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="16.36328125" style="11" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="11" width="7.81640625" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="11" width="25.1796875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="11" width="8.08984375" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="11" width="8.7265625" collapsed="true"/>
+    <col min="5" max="11" style="11" width="16.36328125" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="11" width="10.1796875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="11" width="9.54296875" collapsed="true"/>
+    <col min="14" max="16384" style="11" width="16.36328125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -1629,7 +1651,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1639,7 +1661,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>31</v>
@@ -1648,16 +1670,16 @@
         <v>27</v>
       </c>
       <c r="I2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="L2" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="L2" s="8" t="s">
-        <v>37</v>
       </c>
       <c r="M2" s="8">
         <v>28601</v>
@@ -1673,14 +1695,14 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.1796875" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="5.90625" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="17" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="8" width="12.36328125" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="14" style="8" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="16384" width="8.7265625" style="8" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="8" width="6.0" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="8" width="25.1796875" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="8" width="5.90625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="8" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="8" width="17.0" collapsed="true"/>
+    <col min="6" max="8" bestFit="true" customWidth="true" style="8" width="12.36328125" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="8" width="14.0" collapsed="true"/>
+    <col min="10" max="16384" style="8" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1717,13 +1739,13 @@
         <v>24</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>16</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" s="12">
         <v>20262709</v>
@@ -1735,7 +1757,7 @@
         <v>8000010</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1748,7 +1770,7 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="50.453125" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" customWidth="true" width="50.453125" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1772,11 +1794,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>46</v>
+      <c r="B2" t="s" s="0">
+        <v>61</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1786,7 +1808,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1799,8 +1821,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultColWidth="20.7265625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" style="11" customWidth="1" collapsed="1"/>
-    <col min="2" max="16384" width="20.7265625" style="11" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="11" width="11.08984375" collapsed="true"/>
+    <col min="2" max="16384" style="11" width="20.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1831,7 +1853,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1841,10 +1863,10 @@
         <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1857,8 +1879,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="24.7265625" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="23.7265625" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" customWidth="true" width="24.7265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" width="23.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1878,18 +1900,18 @@
         <v>22</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="244.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
+      <c r="B2" t="s" s="0">
+        <v>63</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1899,7 +1921,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G2" s="13" t="str">
         <f ca="1">F2&amp;TEXT(TODAY()+1,"mm/dd/yyyy")</f>
@@ -1908,7 +1930,7 @@
 Select the date you wish to submit your first payment and it will recur every year on that day,
 Divide your payment plan by...,
 Number of Payments:,Divide the Balance Due into,
-Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 07/07/2026</v>
+Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 07/23/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1921,9 +1943,9 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="30.36328125" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="34" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="23.1796875" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" customWidth="true" width="30.36328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" width="34.0" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" width="23.1796875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
@@ -1943,30 +1965,30 @@
         <v>22</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>8</v>
       </c>
       <c r="K1" s="14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="241" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="B2" t="s">
-        <v>53</v>
+      <c r="B2" t="s" s="0">
+        <v>64</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1976,11 +1998,11 @@
         <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/07/2026</v>
+        <v>07/23/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1997,11 +2019,11 @@
 Number of Payments:,Divide the Balance Due into ,
 Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
 Step 4: Review Payment Plan,
-1 Daily payment of $12.00 on 07/07/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/07/2026</v>
+1 Daily payment of $12.00 on 07/23/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/23/2026</v>
       </c>
       <c r="K2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/07/2026</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/23/2026</v>
       </c>
     </row>
   </sheetData>
@@ -2014,10 +2036,10 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="5" width="8.7265625" style="11" collapsed="1"/>
-    <col min="6" max="6" width="37.6328125" style="11" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="36.90625" style="11" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="8.7265625" style="11" collapsed="1"/>
+    <col min="1" max="5" style="11" width="8.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="11" width="37.6328125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="11" width="36.90625" collapsed="true"/>
+    <col min="8" max="16384" style="11" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2037,7 +2059,7 @@
         <v>22</v>
       </c>
       <c r="F1" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1" s="20" t="s">
         <v>8</v>
@@ -2048,7 +2070,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -2058,7 +2080,7 @@
         <v>25</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">F2&amp;TEXT(TODAY()+1,"mm/dd/yyyy")</f>
@@ -2070,7 +2092,7 @@
 Number of Payments:,Divide the Balance Due into, 
 Individual Amount:,	Repeat this amount until the Balance Due is achieved: $ ,
 Step 4: Review Payment Plan
-1 Quarterly payment of $12.00 on 07/07/2026</v>
+1 Quarterly payment of $12.00 on 07/23/2026</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
+++ b/KatalonData/ABPTestDataDemo/ABPTestData_Demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\ABPTestDataDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BF1C5DC-4DCD-45AC-9483-D31164230F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{543E7AF3-6616-4B36-857C-B6C9FB3D0F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="13" activeTab="14" xr2:uid="{1DD8A320-6572-432F-97F4-1D86BCB29215}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="98">
   <si>
     <t>Result</t>
   </si>
@@ -356,52 +356,91 @@
     <t>Wed Jul 22 18:10:16 IST 2026</t>
   </si>
   <si>
-    <t>Wed Jul 22 18:12:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 18:14:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Please choose another user name</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 21:19:08 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 21:20:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Password must be at least 8 characters long and no more than 16 characters long.,Password must contain at least one alpha character and one numeric character.</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 21:26:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Jul 22 21:37:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 30 15:14:41 IST 2026</t>
+    <t>Thu Jul 30 15:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Aug 13 22:00:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Komal-</t>
+  </si>
+  <si>
+    <t>Username cannot contain any spaces or special characters.</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 16:50:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 16:52:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Password must be at least 8 characters long and no more than 32 characters long.,Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 16:57:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Password must contain at least one alpha character and one numeric character.,The password must also contain at least one special character.</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 16:59:22 IST 2026</t>
   </si>
   <si>
     <t>Fail</t>
   </si>
   <si>
-    <t>Thu Jul 30 15:16:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 30 15:17:48 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 30 15:18:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 30 15:24:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 30 15:24:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Thu Jul 30 15:25:14 IST 2026</t>
+    <t>Tue Aug 25 18:46:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:46:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:46:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:47:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:47:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:47:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:48:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:48:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:48:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:49:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:49:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:49:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:50:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:59:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 18:59:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 19:00:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 19:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Aug 25 21:17:54 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1074,7 @@
       </c>
       <c r="F2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/23/2026</v>
+        <v>08/26/2026</v>
       </c>
       <c r="G2" s="16">
         <v>12</v>
@@ -1051,11 +1090,11 @@
  Individual Amount:,	Repeat this amount until the Balance Due is achieved: $, 
 12.00,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 07/23/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026</v>
+1 Deferred payment of $12.00 on 08/26/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026</v>
       </c>
       <c r="J2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(H2,"0.00")&amp;" starting on "&amp;F2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026</v>
       </c>
     </row>
   </sheetData>
@@ -1130,7 +1169,7 @@
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/23/2026</v>
+        <v>08/26/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1145,7 +1184,7 @@
 Daily,
 Select the date you wish to submit your first payment and it will recur every day after,
 Step 4: Review Payment Plan,
-Daily payments of $12.00 starting on 07/23/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
+Daily payments of $12.00 starting on 08/26/2026,A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1153,7 +1192,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for Daily payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1222,7 +1261,7 @@
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/23/2026</v>
+        <v>08/26/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -1236,7 +1275,7 @@
 Deferred,
 Select the date you wish to submit your payment,
 Step 4: Review Payment Plan,
-1 Deferred payment of $12.00 on 07/23/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
+1 Deferred payment of $12.00 on 08/26/2026,A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1244,7 +1283,7 @@
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Deferred payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2&amp;" ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:"</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 07/23/2026 ,Individual Convenience Fee Amount:,	
+        <v>A Convenience Fee will be added to each transaction issued for 1 Deferred payment of 2.00 starting on 08/26/2026 ,Individual Convenience Fee Amount:,	
 Total Convenience Fees Paid:,	
 Total Paid under this plan:</v>
       </c>
@@ -1281,7 +1320,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1323,7 +1362,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1380,7 +1419,7 @@
         <v>24</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1393,7 +1432,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1401,7 +1440,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>16</v>
@@ -1410,7 +1449,7 @@
         <v>53</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -1418,7 +1457,7 @@
         <v>24</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>16</v>
@@ -1440,7 +1479,8 @@
   <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="42.08984375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="55.1796875"/>
+    <col min="7" max="7" customWidth="true" width="15.6328125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="25" x14ac:dyDescent="0.25">
@@ -1471,7 +1511,7 @@
         <v>24</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8" t="s">
@@ -1481,10 +1521,10 @@
         <v>25</v>
       </c>
       <c r="F2" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="G2" t="s" s="0">
         <v>71</v>
-      </c>
-      <c r="G2" t="s" s="0">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1930,7 +1970,7 @@
 Select the date you wish to submit your first payment and it will recur every year on that day,
 Divide your payment plan by...,
 Number of Payments:,Divide the Balance Due into,
-Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 07/23/2026</v>
+Individual Amount:,Repeat this amount until the Balance Due is achieved: $,1 Annual payment of $12.00 on 08/26/2026</v>
       </c>
     </row>
   </sheetData>
@@ -2002,7 +2042,7 @@
       </c>
       <c r="G2" s="15" t="str">
         <f ca="1">TEXT(TODAY()+1,"mm/dd/yyyy")</f>
-        <v>07/23/2026</v>
+        <v>08/26/2026</v>
       </c>
       <c r="H2" s="16">
         <v>12</v>
@@ -2019,11 +2059,11 @@
 Number of Payments:,Divide the Balance Due into ,
 Individual Amount:,Repeat this amount until the Balance Due is achieved: $, 
 Step 4: Review Payment Plan,
-1 Daily payment of $12.00 on 07/23/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/23/2026</v>
+1 Daily payment of $12.00 on 08/26/2026,A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 08/26/2026</v>
       </c>
       <c r="K2" s="19" t="str">
         <f ca="1">"A Convenience Fee will be added to each transaction issued for 1 Daily payment of "&amp;  TEXT(I2,"0.00")&amp;" starting on "&amp;G2</f>
-        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 07/23/2026</v>
+        <v>A Convenience Fee will be added to each transaction issued for 1 Daily payment of 2.00 starting on 08/26/2026</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2132,7 @@
 Number of Payments:,Divide the Balance Due into, 
 Individual Amount:,	Repeat this amount until the Balance Due is achieved: $ ,
 Step 4: Review Payment Plan
-1 Quarterly payment of $12.00 on 07/23/2026</v>
+1 Quarterly payment of $12.00 on 08/26/2026</v>
       </c>
     </row>
   </sheetData>
